--- a/04-pinecastle-software-grc-program/05-soc2-readiness/artifacts/Pinecastle-SOC2-Readiness-and-Evidence-Tracker.xlsx
+++ b/04-pinecastle-software-grc-program/05-soc2-readiness/artifacts/Pinecastle-SOC2-Readiness-and-Evidence-Tracker.xlsx
@@ -74,7 +74,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border/>
     <border>
       <left style="thin">
@@ -235,11 +235,16 @@
         <color rgb="FFCBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF8EA9C1"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -351,6 +356,13 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1070,28 +1082,28 @@
         </is>
       </c>
       <c r="B9" s="38" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="45" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" s="45">
         <f>SUM(E4:E8)</f>
         <v/>
       </c>
-      <c r="F10">
+      <c r="F10" s="45">
         <f>SUM(F4:F8)</f>
         <v/>
       </c>
-      <c r="G10">
+      <c r="G10" s="45">
         <f>SUM(G4:G8)</f>
         <v/>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="46">
         <f>SUM(E10:G10)&amp;" controls; matches overall: "&amp;IF(SUM(E10:G10)=B3,"Yes","No")</f>
         <v/>
       </c>
@@ -2432,7 +2444,7 @@
         </is>
       </c>
       <c r="E2" s="39" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" s="30" t="inlineStr">
         <is>
@@ -2472,7 +2484,7 @@
         </is>
       </c>
       <c r="E3" s="40" t="n">
-        <v>46285</v>
+        <v>46288</v>
       </c>
       <c r="F3" s="31" t="inlineStr">
         <is>
@@ -2552,7 +2564,7 @@
         </is>
       </c>
       <c r="E5" s="40" t="n">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="F5" s="31" t="inlineStr">
         <is>
@@ -2592,7 +2604,7 @@
         </is>
       </c>
       <c r="E6" s="40" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="F6" s="31" t="inlineStr">
         <is>
@@ -2632,7 +2644,7 @@
         </is>
       </c>
       <c r="E7" s="40" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="F7" s="31" t="inlineStr">
         <is>
@@ -2712,7 +2724,7 @@
         </is>
       </c>
       <c r="E9" s="40" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="F9" s="31" t="inlineStr">
         <is>
@@ -2752,7 +2764,7 @@
         </is>
       </c>
       <c r="E10" s="40" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" s="31" t="inlineStr">
         <is>
@@ -2792,7 +2804,7 @@
         </is>
       </c>
       <c r="E11" s="41" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="F11" s="32" t="inlineStr">
         <is>
@@ -2872,7 +2884,7 @@
         </is>
       </c>
       <c r="E13" s="41" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="F13" s="32" t="inlineStr">
         <is>
@@ -3056,7 +3068,7 @@
         </is>
       </c>
       <c r="H2" s="39" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="I2" s="30" t="inlineStr">
         <is>
@@ -3101,7 +3113,7 @@
         </is>
       </c>
       <c r="H3" s="40" t="n">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="I3" s="31" t="inlineStr">
         <is>
@@ -3146,7 +3158,7 @@
         </is>
       </c>
       <c r="H4" s="40" t="n">
-        <v>46341</v>
+        <v>46338</v>
       </c>
       <c r="I4" s="31" t="inlineStr">
         <is>
@@ -3191,7 +3203,7 @@
         </is>
       </c>
       <c r="H5" s="40" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="I5" s="31" t="inlineStr">
         <is>
@@ -3236,7 +3248,7 @@
         </is>
       </c>
       <c r="H6" s="41" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="I6" s="32" t="inlineStr">
         <is>
@@ -3281,7 +3293,7 @@
         </is>
       </c>
       <c r="H7" s="41" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="I7" s="32" t="inlineStr">
         <is>
@@ -3381,7 +3393,7 @@
         </is>
       </c>
       <c r="D2" s="39" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="E2" s="30" t="inlineStr">
         <is>
@@ -3421,7 +3433,7 @@
         </is>
       </c>
       <c r="D3" s="40" t="n">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="E3" s="31" t="inlineStr">
         <is>
@@ -3461,7 +3473,7 @@
         </is>
       </c>
       <c r="D4" s="40" t="n">
-        <v>46341</v>
+        <v>46338</v>
       </c>
       <c r="E4" s="31" t="inlineStr">
         <is>
@@ -3501,7 +3513,7 @@
         </is>
       </c>
       <c r="D5" s="40" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="E5" s="31" t="inlineStr">
         <is>
@@ -3541,7 +3553,7 @@
         </is>
       </c>
       <c r="D6" s="41" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="E6" s="32" t="inlineStr">
         <is>
@@ -3581,7 +3593,7 @@
         </is>
       </c>
       <c r="D7" s="41" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="E7" s="32" t="inlineStr">
         <is>
@@ -3745,7 +3757,7 @@
         </is>
       </c>
       <c r="D7" s="42" t="n">
-        <v>46356</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="8">
@@ -3799,7 +3811,7 @@
         </is>
       </c>
       <c r="B10" s="41" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
